--- a/data/trans_bre/P19-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P19-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,1; 20,8</t>
+          <t>9,38; 20,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 13,98</t>
+          <t>1,25; 14,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 12,79</t>
+          <t>-1,85; 11,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 14,46</t>
+          <t>-6,73; 14,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,23; 91,53</t>
+          <t>34,15; 93,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 51,49</t>
+          <t>3,7; 51,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 35,44</t>
+          <t>-4,41; 34,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,4; 64,62</t>
+          <t>-20,03; 66,4</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 11,5</t>
+          <t>1,35; 11,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 9,11</t>
+          <t>-1,32; 9,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 12,96</t>
+          <t>1,73; 13,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 7,52</t>
+          <t>-12,86; 7,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,17; 45,94</t>
+          <t>4,58; 45,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 33,4</t>
+          <t>-4,14; 33,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,75; 41,15</t>
+          <t>4,08; 40,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,78; 26,95</t>
+          <t>-38,78; 26,19</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 12,21</t>
+          <t>1,54; 11,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,91; 13,72</t>
+          <t>3,5; 13,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 13,16</t>
+          <t>2,39; 12,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,69; 16,37</t>
+          <t>6,1; 16,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,99; 53,07</t>
+          <t>5,7; 50,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,2; 58,88</t>
+          <t>12,64; 57,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,11; 50,94</t>
+          <t>7,62; 48,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,37; 66,07</t>
+          <t>19,12; 66,27</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 15,64</t>
+          <t>4,04; 15,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 11,64</t>
+          <t>0,47; 12,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 11,75</t>
+          <t>0,87; 11,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,93; 35,64</t>
+          <t>6,62; 34,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,06; 63,64</t>
+          <t>12,96; 66,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 48,96</t>
+          <t>1,63; 51,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 42,35</t>
+          <t>2,0; 41,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,93; 374,57</t>
+          <t>21,25; 329,17</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 11,59</t>
+          <t>-0,89; 11,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 12,55</t>
+          <t>1,44; 13,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 10,19</t>
+          <t>-2,85; 9,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,03; 13,22</t>
+          <t>3,42; 12,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 53,96</t>
+          <t>-3,17; 55,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,83; 70,54</t>
+          <t>4,77; 71,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 41,06</t>
+          <t>-9,82; 38,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,1; 58,19</t>
+          <t>11,77; 52,89</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 6,84</t>
+          <t>-5,36; 6,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,32; 14,65</t>
+          <t>1,3; 15,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,59; 16,34</t>
+          <t>3,25; 16,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,14; 0,75</t>
+          <t>-22,47; 0,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-22,66; 38,24</t>
+          <t>-22,52; 36,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,19; 101,4</t>
+          <t>6,16; 100,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,13; 100,34</t>
+          <t>13,42; 97,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-72,44; 2,57</t>
+          <t>-76,22; 3,07</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 6,43</t>
+          <t>-5,52; 6,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 9,25</t>
+          <t>-1,11; 9,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 9,35</t>
+          <t>-2,36; 9,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 2,95</t>
+          <t>-5,56; 2,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-32,17; 65,92</t>
+          <t>-32,32; 65,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 154,4</t>
+          <t>-10,88; 149,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 82,83</t>
+          <t>-15,22; 84,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-30,31; 24,66</t>
+          <t>-31,72; 23,51</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,39; 8,56</t>
+          <t>4,29; 8,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,34; 8,05</t>
+          <t>3,26; 7,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,84</t>
+          <t>3,2; 7,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 10,45</t>
+          <t>-0,29; 10,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,09; 35,84</t>
+          <t>16,31; 36,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,85; 34,15</t>
+          <t>12,91; 32,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,38; 28,27</t>
+          <t>10,67; 27,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,62; 49,22</t>
+          <t>-0,46; 46,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P19-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,27</t>
+          <t>3,8</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,38; 20,86</t>
+          <t>9,51; 21,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 14,27</t>
+          <t>1,01; 13,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 11,89</t>
+          <t>-1,61; 12,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 14,89</t>
+          <t>-7,26; 13,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,15; 93,53</t>
+          <t>33,09; 96,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 51,36</t>
+          <t>2,4; 48,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 34,0</t>
+          <t>-3,86; 33,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,03; 66,4</t>
+          <t>-20,92; 61,09</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,15</t>
+          <t>4,47</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-3,74%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 11,33</t>
+          <t>0,92; 11,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 9,21</t>
+          <t>-1,24; 8,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 13,0</t>
+          <t>2,04; 12,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 7,42</t>
+          <t>-2,34; 10,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,58; 45,57</t>
+          <t>2,46; 45,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 33,5</t>
+          <t>-3,9; 32,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,08; 40,64</t>
+          <t>5,26; 38,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,78; 26,19</t>
+          <t>-7,27; 45,11</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,32</t>
+          <t>11,68</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>44,07%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 11,68</t>
+          <t>1,53; 12,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,5; 13,4</t>
+          <t>3,33; 13,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 12,54</t>
+          <t>2,33; 12,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,1; 16,26</t>
+          <t>6,57; 16,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,7; 50,44</t>
+          <t>5,48; 51,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,64; 57,05</t>
+          <t>11,52; 57,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,62; 48,28</t>
+          <t>7,66; 50,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,12; 66,27</t>
+          <t>22,37; 72,34</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,39</t>
+          <t>6,05</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 15,67</t>
+          <t>4,5; 16,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 12,23</t>
+          <t>0,18; 11,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 11,55</t>
+          <t>0,23; 11,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,62; 34,94</t>
+          <t>1,43; 10,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,96; 66,12</t>
+          <t>14,64; 69,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 51,2</t>
+          <t>0,32; 49,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 41,06</t>
+          <t>0,7; 40,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,25; 329,17</t>
+          <t>4,36; 39,81</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,43</t>
+          <t>8,38</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 11,79</t>
+          <t>-0,78; 11,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 13,2</t>
+          <t>0,86; 12,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 9,68</t>
+          <t>-2,14; 10,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 12,42</t>
+          <t>3,72; 12,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 55,5</t>
+          <t>-3,46; 51,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,77; 71,04</t>
+          <t>3,57; 71,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 38,97</t>
+          <t>-7,09; 42,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,77; 52,89</t>
+          <t>12,67; 55,35</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-9,59</t>
+          <t>-0,61</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-35,92%</t>
+          <t>-2,27%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 6,46</t>
+          <t>-5,88; 6,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,3; 15,32</t>
+          <t>1,99; 15,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,25; 16,73</t>
+          <t>3,71; 16,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-22,47; 0,78</t>
+          <t>-5,38; 4,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-22,52; 36,71</t>
+          <t>-22,72; 39,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,16; 100,11</t>
+          <t>7,47; 104,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,42; 97,73</t>
+          <t>14,76; 103,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-76,22; 3,07</t>
+          <t>-18,27; 17,37</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,01</t>
+          <t>-1,38</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-6,85%</t>
+          <t>-9,01%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 6,62</t>
+          <t>-5,58; 6,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 9,27</t>
+          <t>-1,53; 8,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 9,41</t>
+          <t>-2,18; 9,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 2,97</t>
+          <t>-5,8; 3,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-32,32; 65,11</t>
+          <t>-34,16; 66,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 149,52</t>
+          <t>-12,42; 143,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 84,76</t>
+          <t>-13,64; 92,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-31,72; 23,51</t>
+          <t>-32,0; 24,71</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,77</t>
+          <t>4,82</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,29; 8,66</t>
+          <t>4,14; 8,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,26; 7,68</t>
+          <t>3,25; 7,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,2; 7,71</t>
+          <t>3,11; 7,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 10,18</t>
+          <t>2,68; 6,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,31; 36,05</t>
+          <t>15,76; 35,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,91; 32,61</t>
+          <t>12,91; 32,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,67; 27,87</t>
+          <t>10,24; 28,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 46,89</t>
+          <t>9,66; 28,26</t>
         </is>
       </c>
     </row>
